--- a/inquiries.xlsx
+++ b/inquiries.xlsx
@@ -628,7 +628,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>The Long Table — inquiry log</t>
+          <t>Azi Catering — inquiry log</t>
         </is>
       </c>
     </row>
